--- a/processo_2/synthetic_proposals/PROPOSTA_005/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_005/ficha_pontuacao.xlsx
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>1.5</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -804,12 +804,12 @@
           <t>Revista Científica Avançada 1</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>79%</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2914-1491</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -981,7 +981,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G28" t="inlineStr"/>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1075,7 +1075,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1141,17 +1141,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr"/>
     </row>
@@ -1187,17 +1187,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G37" t="inlineStr"/>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1279,14 +1279,18 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" t="n">
         <v>3</v>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
       <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1298,17 +1302,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>1.5</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
@@ -1321,7 +1325,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1503,13 +1507,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G51" t="inlineStr"/>
     </row>
@@ -1539,17 +1543,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>5</v>
       </c>
       <c r="F53" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G53" t="inlineStr"/>
     </row>
@@ -1562,7 +1566,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1608,7 +1612,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1631,17 +1635,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G57" t="inlineStr"/>
     </row>
@@ -1772,13 +1776,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
         <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G64" t="inlineStr"/>
     </row>
@@ -1818,13 +1822,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G66" t="inlineStr"/>
     </row>
@@ -1839,7 +1843,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -1853,7 +1857,9 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>42.5</v>
+      </c>
       <c r="G68" t="inlineStr"/>
     </row>
   </sheetData>
